--- a/templates/attendance_list_template.xlsx
+++ b/templates/attendance_list_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D0A92F-2CA1-4461-A33B-E9C97698E960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF0027A-2EAD-4A25-A246-C2CD181B8EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53E1B85A-68AA-416C-800A-B9F1320CDB60}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t>Nome</t>
   </si>
   <si>
-    <t>Email</t>
-  </si>
-  <si>
     <t>QUADRO ATIVO</t>
   </si>
   <si>
@@ -70,12 +67,15 @@
   <si>
     <t>Comparece</t>
   </si>
+  <si>
+    <t>Motivo</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,6 +170,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3" tint="0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -845,7 +853,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1253,7 +1261,7 @@
   <sheetData>
     <row r="2" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="67" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="67"/>
       <c r="D2" s="67"/>
@@ -1355,10 +1363,10 @@
       <c r="K9" s="56"/>
       <c r="L9" s="56"/>
       <c r="M9" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N9" s="37" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="2:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1426,7 +1434,7 @@
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="55" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" s="55"/>
       <c r="D15" s="55"/>
@@ -1473,10 +1481,10 @@
       <c r="K17" s="56"/>
       <c r="L17" s="56"/>
       <c r="M17" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N17" s="37" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2999,7 +3007,7 @@
     </row>
     <row r="120" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B120" s="55" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C120" s="55"/>
       <c r="D120" s="55"/>
@@ -3038,10 +3046,10 @@
       <c r="K122" s="56"/>
       <c r="L122" s="56"/>
       <c r="M122" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N122" s="37" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="2:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3381,7 +3389,7 @@
     </row>
     <row r="146" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B146" s="55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C146" s="55"/>
       <c r="D146" s="55"/>
@@ -3430,10 +3438,10 @@
       <c r="K148" s="56"/>
       <c r="L148" s="56"/>
       <c r="M148" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N148" s="37" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149" spans="2:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3608,7 +3616,7 @@
     </row>
     <row r="161" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B161" s="55" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C161" s="55"/>
       <c r="D161" s="55"/>
@@ -3645,10 +3653,10 @@
       <c r="K163" s="56"/>
       <c r="L163" s="56"/>
       <c r="M163" s="36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N163" s="37" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="164" spans="2:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/templates/attendance_list_template.xlsx
+++ b/templates/attendance_list_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF0027A-2EAD-4A25-A246-C2CD181B8EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC3D643-8D5C-4735-8FF7-EEC49A32A20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53E1B85A-68AA-416C-800A-B9F1320CDB60}"/>
   </bookViews>
@@ -199,7 +199,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -618,12 +618,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -854,6 +863,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1246,7 +1267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA636C58-DBD3-4D00-B974-AA60A60DBC67}">
-  <dimension ref="A2:P184"/>
+  <dimension ref="A2:P185"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
@@ -3961,6 +3982,21 @@
       <c r="L184" s="54"/>
       <c r="M184" s="9"/>
       <c r="N184" s="10"/>
+    </row>
+    <row r="185" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B185" s="71"/>
+      <c r="C185" s="72"/>
+      <c r="D185" s="72"/>
+      <c r="E185" s="72"/>
+      <c r="F185" s="73"/>
+      <c r="G185" s="73"/>
+      <c r="H185" s="73"/>
+      <c r="I185" s="73"/>
+      <c r="J185" s="73"/>
+      <c r="K185" s="73"/>
+      <c r="L185" s="73"/>
+      <c r="M185" s="74"/>
+      <c r="N185" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="329">
